--- a/resultados/santoantoniodoparaiso/erros_varredura.xlsx
+++ b/resultados/santoantoniodoparaiso/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,6 +2268,370 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hnPzT/</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:45:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RBPwj/</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-10 17:13:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dn--z/</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:07:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GR-ox/</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:20:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dKwx/</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:57:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nnPj-/</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>4</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:29:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Chwj/</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:37:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hKww/</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-10 20:06:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ChTAL/</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-10 22:23:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/?locale=es_419</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>404</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:14:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/ouvidoria/cadastro</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:01:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/newsletter</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-11 11:27:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/qqTwA/</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>5</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-11 14:39:33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/santoantoniodoparaiso/erros_varredura.xlsx
+++ b/resultados/santoantoniodoparaiso/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F905"/>
+  <dimension ref="A1:F1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25760,6 +25760,2862 @@
         </is>
       </c>
     </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nKjxT/</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D906" t="n">
+        <v>0</v>
+      </c>
+      <c r="E906" t="n">
+        <v>7</v>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dhLL/</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D907" t="n">
+        <v>0</v>
+      </c>
+      <c r="E907" t="n">
+        <v>7</v>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/shjxw/</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D908" t="n">
+        <v>0</v>
+      </c>
+      <c r="E908" t="n">
+        <v>7</v>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/KGjxz/</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D909" t="n">
+        <v>0</v>
+      </c>
+      <c r="E909" t="n">
+        <v>7</v>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GnjxL/</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D910" t="n">
+        <v>0</v>
+      </c>
+      <c r="E910" t="n">
+        <v>7</v>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/CGjxw/</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D911" t="n">
+        <v>0</v>
+      </c>
+      <c r="E911" t="n">
+        <v>7</v>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/dnjxz/</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D912" t="n">
+        <v>0</v>
+      </c>
+      <c r="E912" t="n">
+        <v>7</v>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/qGLL/</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D913" t="n">
+        <v>0</v>
+      </c>
+      <c r="E913" t="n">
+        <v>7</v>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:06:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KqTL-/</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D914" t="n">
+        <v>0</v>
+      </c>
+      <c r="E914" t="n">
+        <v>7</v>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nsTjL/</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D915" t="n">
+        <v>0</v>
+      </c>
+      <c r="E915" t="n">
+        <v>7</v>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:21:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CRTjP/</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D916" t="n">
+        <v>0</v>
+      </c>
+      <c r="E916" t="n">
+        <v>7</v>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:21:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sCT-x/</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D917" t="n">
+        <v>0</v>
+      </c>
+      <c r="E917" t="n">
+        <v>7</v>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:33:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hRT-x/</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D918" t="n">
+        <v>0</v>
+      </c>
+      <c r="E918" t="n">
+        <v>7</v>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:33:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GBT-A/</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D919" t="n">
+        <v>0</v>
+      </c>
+      <c r="E919" t="n">
+        <v>7</v>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:33:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/snT-A/</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D920" t="n">
+        <v>0</v>
+      </c>
+      <c r="E920" t="n">
+        <v>7</v>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:33:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RBToP/</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D921" t="n">
+        <v>0</v>
+      </c>
+      <c r="E921" t="n">
+        <v>7</v>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:33:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qqTxT/</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D922" t="n">
+        <v>0</v>
+      </c>
+      <c r="E922" t="n">
+        <v>7</v>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:36:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dGTxT/</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D923" t="n">
+        <v>0</v>
+      </c>
+      <c r="E923" t="n">
+        <v>7</v>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:36:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sGTxL/</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D924" t="n">
+        <v>0</v>
+      </c>
+      <c r="E924" t="n">
+        <v>7</v>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:37:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GsTxP/</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D925" t="n">
+        <v>0</v>
+      </c>
+      <c r="E925" t="n">
+        <v>7</v>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:37:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hhTxP/</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D926" t="n">
+        <v>0</v>
+      </c>
+      <c r="E926" t="n">
+        <v>7</v>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:37:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GqTxj/</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D927" t="n">
+        <v>0</v>
+      </c>
+      <c r="E927" t="n">
+        <v>7</v>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:37:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qhoLL/</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D928" t="n">
+        <v>0</v>
+      </c>
+      <c r="E928" t="n">
+        <v>7</v>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:40:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RhoLT/</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D929" t="n">
+        <v>0</v>
+      </c>
+      <c r="E929" t="n">
+        <v>7</v>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:40:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KdoLT/</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D930" t="n">
+        <v>0</v>
+      </c>
+      <c r="E930" t="n">
+        <v>7</v>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:40:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dhoLz/</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D931" t="n">
+        <v>0</v>
+      </c>
+      <c r="E931" t="n">
+        <v>7</v>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:40:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nnoLz/</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D932" t="n">
+        <v>0</v>
+      </c>
+      <c r="E932" t="n">
+        <v>7</v>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:40:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nnoLw/</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D933" t="n">
+        <v>0</v>
+      </c>
+      <c r="E933" t="n">
+        <v>7</v>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:40:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GBoLw/</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D934" t="n">
+        <v>0</v>
+      </c>
+      <c r="E934" t="n">
+        <v>7</v>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:40:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dKoTA/</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D935" t="n">
+        <v>0</v>
+      </c>
+      <c r="E935" t="n">
+        <v>7</v>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:40:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KKoTA/</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D936" t="n">
+        <v>0</v>
+      </c>
+      <c r="E936" t="n">
+        <v>7</v>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:40:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ssoTx/</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D937" t="n">
+        <v>0</v>
+      </c>
+      <c r="E937" t="n">
+        <v>7</v>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KRoT-/</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D938" t="n">
+        <v>0</v>
+      </c>
+      <c r="E938" t="n">
+        <v>7</v>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:41:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CsoT-/</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D939" t="n">
+        <v>0</v>
+      </c>
+      <c r="E939" t="n">
+        <v>7</v>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>2026-08-20 13:41:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hGPLw/</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D940" t="n">
+        <v>0</v>
+      </c>
+      <c r="E940" t="n">
+        <v>7</v>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>2026-08-20 14:33:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ndTLL/</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D941" t="n">
+        <v>0</v>
+      </c>
+      <c r="E941" t="n">
+        <v>7</v>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:09:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RGTLL/</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D942" t="n">
+        <v>0</v>
+      </c>
+      <c r="E942" t="n">
+        <v>7</v>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:09:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sqTLT/</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D943" t="n">
+        <v>0</v>
+      </c>
+      <c r="E943" t="n">
+        <v>7</v>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:09:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ssTLT/</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D944" t="n">
+        <v>0</v>
+      </c>
+      <c r="E944" t="n">
+        <v>7</v>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:09:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hKTLo/</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D945" t="n">
+        <v>0</v>
+      </c>
+      <c r="E945" t="n">
+        <v>7</v>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:09:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CKTLo/</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D946" t="n">
+        <v>0</v>
+      </c>
+      <c r="E946" t="n">
+        <v>7</v>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GBTL-/</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D947" t="n">
+        <v>0</v>
+      </c>
+      <c r="E947" t="n">
+        <v>7</v>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hRTLx/</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D948" t="n">
+        <v>0</v>
+      </c>
+      <c r="E948" t="n">
+        <v>7</v>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ddTLx/</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D949" t="n">
+        <v>0</v>
+      </c>
+      <c r="E949" t="n">
+        <v>7</v>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qKTPw/</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D950" t="n">
+        <v>0</v>
+      </c>
+      <c r="E950" t="n">
+        <v>7</v>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hKTLA/</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D951" t="n">
+        <v>0</v>
+      </c>
+      <c r="E951" t="n">
+        <v>7</v>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RnTLA/</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D952" t="n">
+        <v>0</v>
+      </c>
+      <c r="E952" t="n">
+        <v>7</v>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CKTPz/</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D953" t="n">
+        <v>0</v>
+      </c>
+      <c r="E953" t="n">
+        <v>7</v>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:10:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GdTPP/</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D954" t="n">
+        <v>0</v>
+      </c>
+      <c r="E954" t="n">
+        <v>7</v>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:13:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nnTPP/</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D955" t="n">
+        <v>0</v>
+      </c>
+      <c r="E955" t="n">
+        <v>7</v>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:13:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KKTPL/</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D956" t="n">
+        <v>0</v>
+      </c>
+      <c r="E956" t="n">
+        <v>7</v>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:13:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nsTPo/</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D957" t="n">
+        <v>0</v>
+      </c>
+      <c r="E957" t="n">
+        <v>7</v>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:13:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KRTPo/</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D958" t="n">
+        <v>0</v>
+      </c>
+      <c r="E958" t="n">
+        <v>7</v>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:13:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nGTP-/</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D959" t="n">
+        <v>0</v>
+      </c>
+      <c r="E959" t="n">
+        <v>7</v>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:13:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nCTPx/</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D960" t="n">
+        <v>0</v>
+      </c>
+      <c r="E960" t="n">
+        <v>7</v>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:14:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qdToL/</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D961" t="n">
+        <v>0</v>
+      </c>
+      <c r="E961" t="n">
+        <v>7</v>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:26:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hGToo/</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D962" t="n">
+        <v>0</v>
+      </c>
+      <c r="E962" t="n">
+        <v>7</v>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:26:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dRToo/</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D963" t="n">
+        <v>0</v>
+      </c>
+      <c r="E963" t="n">
+        <v>7</v>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:26:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GGToj/</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D964" t="n">
+        <v>0</v>
+      </c>
+      <c r="E964" t="n">
+        <v>7</v>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:26:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RnTo-/</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D965" t="n">
+        <v>0</v>
+      </c>
+      <c r="E965" t="n">
+        <v>7</v>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:33:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qqTxj/</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D966" t="n">
+        <v>0</v>
+      </c>
+      <c r="E966" t="n">
+        <v>7</v>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:35:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KdTxz/</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D967" t="n">
+        <v>0</v>
+      </c>
+      <c r="E967" t="n">
+        <v>7</v>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:38:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CCTxz/</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D968" t="n">
+        <v>0</v>
+      </c>
+      <c r="E968" t="n">
+        <v>7</v>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:38:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qKTxw/</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>0</v>
+      </c>
+      <c r="E969" t="n">
+        <v>7</v>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:38:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sRTxw/</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>0</v>
+      </c>
+      <c r="E970" t="n">
+        <v>7</v>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:38:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KqzAP/</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>0</v>
+      </c>
+      <c r="E971" t="n">
+        <v>7</v>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hdzAP/</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>0</v>
+      </c>
+      <c r="E972" t="n">
+        <v>7</v>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sGzAL/</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D973" t="n">
+        <v>0</v>
+      </c>
+      <c r="E973" t="n">
+        <v>7</v>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hRzAT/</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>0</v>
+      </c>
+      <c r="E974" t="n">
+        <v>7</v>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KKzAT/</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>0</v>
+      </c>
+      <c r="E975" t="n">
+        <v>7</v>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KGzAz/</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D976" t="n">
+        <v>0</v>
+      </c>
+      <c r="E976" t="n">
+        <v>7</v>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hdzAz/</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D977" t="n">
+        <v>0</v>
+      </c>
+      <c r="E977" t="n">
+        <v>7</v>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:39:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nGTww/</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D978" t="n">
+        <v>0</v>
+      </c>
+      <c r="E978" t="n">
+        <v>7</v>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:40:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CqzAx/</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D979" t="n">
+        <v>0</v>
+      </c>
+      <c r="E979" t="n">
+        <v>7</v>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:40:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CRzA-/</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D980" t="n">
+        <v>0</v>
+      </c>
+      <c r="E980" t="n">
+        <v>7</v>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ndzA-/</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D981" t="n">
+        <v>0</v>
+      </c>
+      <c r="E981" t="n">
+        <v>7</v>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nsTwT/</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D982" t="n">
+        <v>0</v>
+      </c>
+      <c r="E982" t="n">
+        <v>7</v>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hnTwz/</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D983" t="n">
+        <v>0</v>
+      </c>
+      <c r="E983" t="n">
+        <v>7</v>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nKTwz/</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D984" t="n">
+        <v>0</v>
+      </c>
+      <c r="E984" t="n">
+        <v>7</v>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ChzAA/</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D985" t="n">
+        <v>0</v>
+      </c>
+      <c r="E985" t="n">
+        <v>7</v>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qqzAA/</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D986" t="n">
+        <v>0</v>
+      </c>
+      <c r="E986" t="n">
+        <v>7</v>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:41:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RGTwj/</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D987" t="n">
+        <v>0</v>
+      </c>
+      <c r="E987" t="n">
+        <v>7</v>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:44:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RKTwP/</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D988" t="n">
+        <v>0</v>
+      </c>
+      <c r="E988" t="n">
+        <v>7</v>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hKTwP/</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D989" t="n">
+        <v>0</v>
+      </c>
+      <c r="E989" t="n">
+        <v>7</v>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:44:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dCTwx/</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D990" t="n">
+        <v>0</v>
+      </c>
+      <c r="E990" t="n">
+        <v>7</v>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:44:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dBTzT/</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D991" t="n">
+        <v>0</v>
+      </c>
+      <c r="E991" t="n">
+        <v>7</v>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qdTzL/</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D992" t="n">
+        <v>0</v>
+      </c>
+      <c r="E992" t="n">
+        <v>7</v>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hdTzL/</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D993" t="n">
+        <v>0</v>
+      </c>
+      <c r="E993" t="n">
+        <v>7</v>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KCTzP/</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D994" t="n">
+        <v>0</v>
+      </c>
+      <c r="E994" t="n">
+        <v>7</v>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qBTzP/</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D995" t="n">
+        <v>0</v>
+      </c>
+      <c r="E995" t="n">
+        <v>7</v>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KsTzj/</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D996" t="n">
+        <v>0</v>
+      </c>
+      <c r="E996" t="n">
+        <v>7</v>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nBTzj/</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D997" t="n">
+        <v>0</v>
+      </c>
+      <c r="E997" t="n">
+        <v>7</v>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KhTzo/</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D998" t="n">
+        <v>0</v>
+      </c>
+      <c r="E998" t="n">
+        <v>7</v>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dsTzo/</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D999" t="n">
+        <v>0</v>
+      </c>
+      <c r="E999" t="n">
+        <v>7</v>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sCTz-/</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:47:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hqTTx/</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:55:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GdTTA/</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:57:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GdTLw/</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:57:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ChTLw/</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:57:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dRTLT/</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>2026-08-20 17:00:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sBTLo/</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>2026-08-20 17:00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ddTLA/</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>2026-08-20 17:03:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/santoantoniodoparaiso/erros_varredura.xlsx
+++ b/resultados/santoantoniodoparaiso/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6300,6 +6300,8154 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/sn-z-o/</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>7</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/dC-zxw/</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>7</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/qs-zxT/</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>7</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/nC-zxo/</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>7</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/nR-zx-/</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>7</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/hh-zxx/</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>7</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/dR-zAw/</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
+        <v>7</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/RG-zAT/</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>7</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/dB-zAL/</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>7</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/dn-zAP/</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>7</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/KG-zAj/</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>7</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/hR-zA-/</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>7</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/sC-zAA/</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>7</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/GK-Tww/</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>7</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:01:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/CC-TwT/</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>7</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:02:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/Gn-Twx/</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>7</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:02:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/hd-TzL/</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>7</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:03:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/dh-L-/</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>7</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:04:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/dR-Lj/</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>7</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:04:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/sR-Lw/</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>7</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:04:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/qG-TA/</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>7</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/KG-zL/</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>7</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:05:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/qs-wx/</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>7</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:09:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/RRoAT/</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>7</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/KCoAz/</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>7</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:16:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/arquivos/GGxAL-/</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>7</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:17:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/arquivos/shxAjz/</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>7</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:18:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/arquivos/CsxAPL/</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>7</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/arquivos/dhxAPP/</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>7</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:18:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/arquivos/KdxxTz/</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>8</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/arquivos/RsxxLx/</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>8</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:19:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/arquivos/Chx-Aw/</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>8</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:19:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/arquivos/RBx-xA/</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>8</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:19:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dBoPw/</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>8</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:21:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/CsoPw/</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>8</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:21:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hqzo/</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>8</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:22:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Gnzz/</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>8</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qszw/</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>8</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Gdwx/</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>8</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Rswx/</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>8</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Chwo/</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>8</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qhwj/</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>8</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qGwT/</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>8</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Cswz/</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>8</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KKxA-/</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>8</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hnxAo/</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>8</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:23:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GhxAj/</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>8</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:24:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GCxAL/</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>8</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CdxAL/</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>8</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:24:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hsxAT/</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>8</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:24:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dsxAz/</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>8</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:24:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Csxxo/</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>8</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:26:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hdxxL/</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>8</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:26:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qRxxL/</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>8</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:26:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CsxxT/</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>8</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:26:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nKxxz/</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>8</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:26:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hBxxz/</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>8</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:26:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GRxxw/</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>8</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:26:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nGx-x/</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>8</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:27:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qKx-j/</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>8</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:27:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Csx-j/</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>8</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:27:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GKx-P/</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>8</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:27:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KCx-P/</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>8</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:27:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KRx-w/</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>8</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ssxoA/</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>8</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nKxox/</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>8</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hKxox/</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>8</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Ghxo-/</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>8</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sdxo-/</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>8</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Rq-oj/</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>8</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RR-oj/</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>8</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GB-oP/</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>8</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sq-oP/</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" t="n">
+        <v>8</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dn-oL/</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>8</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qR-oT/</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>8</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ss-oz/</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>8</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ss-jx/</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>8</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hK-jx/</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>8</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:29:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hG-j-/</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>8</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dh-jo/</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="n">
+        <v>8</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:30:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RB-jj/</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>8</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:30:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RB-jL/</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>8</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:30:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Kd-jz/</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" t="n">
+        <v>8</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:30:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RK-jw/</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>8</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:30:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Gsowo/</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>8</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:31:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Rdj--/</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>8</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:34:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Kdj--/</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>0</v>
+      </c>
+      <c r="E297" t="n">
+        <v>8</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:34:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GGLjz/</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>8</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:36:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/KdoLT/</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>8</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:36:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/nRoPT/</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>8</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:46:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/KRjxT/</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>8</v>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:46:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dGjAx/</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>8</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:47:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/ddLPj/</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>8</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:50:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/dCLPo/</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
+        <v>8</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:50:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/sBLP-/</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>0</v>
+      </c>
+      <c r="E305" t="n">
+        <v>8</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:51:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Kqow-/</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>0</v>
+      </c>
+      <c r="E306" t="n">
+        <v>8</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:55:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/qGow-/</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" t="n">
+        <v>8</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:55:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos-anexos/RnxxwT/</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>0</v>
+      </c>
+      <c r="E308" t="n">
+        <v>8</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:55:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos-anexos/KnxxwL/</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>0</v>
+      </c>
+      <c r="E309" t="n">
+        <v>8</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:55:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos-anexos/RGxxAx/</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>0</v>
+      </c>
+      <c r="E310" t="n">
+        <v>8</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:55:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos-anexos/qRxAww/</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>0</v>
+      </c>
+      <c r="E311" t="n">
+        <v>8</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:55:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos-anexos/sKxAwz/</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" t="n">
+        <v>8</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:55:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos-anexos/KhxxAA/</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" t="n">
+        <v>8</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:57:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos-anexos/shxALT/</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>0</v>
+      </c>
+      <c r="E314" t="n">
+        <v>8</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:57:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos/nBL-w/</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
+      </c>
+      <c r="E315" t="n">
+        <v>8</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:57:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos/qKPzo/</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>8</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:01:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/concursos/RsPjx/</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+      <c r="E317" t="n">
+        <v>8</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:01:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GhxooL/</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>0</v>
+      </c>
+      <c r="E318" t="n">
+        <v>8</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GhxooL/</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>0</v>
+      </c>
+      <c r="E319" t="n">
+        <v>8</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:01:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GCPz-/</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>0</v>
+      </c>
+      <c r="E320" t="n">
+        <v>8</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:01:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/CqPzx/</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>0</v>
+      </c>
+      <c r="E321" t="n">
+        <v>8</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CGo/</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>0</v>
+      </c>
+      <c r="E322" t="n">
+        <v>8</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:01:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dnL/</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>0</v>
+      </c>
+      <c r="E323" t="n">
+        <v>8</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:01:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/Cq-TPx/</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>0</v>
+      </c>
+      <c r="E324" t="n">
+        <v>8</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:02:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/Kd-TjP/</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>8</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:02:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/dC-Toz/</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>8</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:04:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/nn-ToT/</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>0</v>
+      </c>
+      <c r="E327" t="n">
+        <v>8</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:04:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/Gd-ToL/</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>0</v>
+      </c>
+      <c r="E328" t="n">
+        <v>8</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:04:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/qB-ToP/</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>0</v>
+      </c>
+      <c r="E329" t="n">
+        <v>8</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:04:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/diario-oficial/GR-Toj/</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>0</v>
+      </c>
+      <c r="E330" t="n">
+        <v>8</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:04:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/arquivos/KsxALT/</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>0</v>
+      </c>
+      <c r="E331" t="n">
+        <v>9</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:05:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qRxjo/</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>0</v>
+      </c>
+      <c r="E332" t="n">
+        <v>9</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CCxjj/</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>0</v>
+      </c>
+      <c r="E333" t="n">
+        <v>9</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:05:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/nRxjj/</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>0</v>
+      </c>
+      <c r="E334" t="n">
+        <v>9</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:05:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KqxjT/</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" t="n">
+        <v>9</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:05:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ssxzP/</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>0</v>
+      </c>
+      <c r="E336" t="n">
+        <v>9</v>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:05:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/Kdx-oT/</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D337" t="n">
+        <v>0</v>
+      </c>
+      <c r="E337" t="n">
+        <v>9</v>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:07:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/GsLP-/</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>0</v>
+      </c>
+      <c r="E338" t="n">
+        <v>9</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:10:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/hqLjP/</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D339" t="n">
+        <v>0</v>
+      </c>
+      <c r="E339" t="n">
+        <v>9</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:10:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/hhxj-A/</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D340" t="n">
+        <v>0</v>
+      </c>
+      <c r="E340" t="n">
+        <v>9</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:10:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/dqxxw-/</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D341" t="n">
+        <v>0</v>
+      </c>
+      <c r="E341" t="n">
+        <v>9</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:12:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GBxxzw/</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>9</v>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/hGx-Pz/</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>9</v>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/Chx-Az/</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>0</v>
+      </c>
+      <c r="E344" t="n">
+        <v>9</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:12:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/RRxxPL/</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>0</v>
+      </c>
+      <c r="E345" t="n">
+        <v>9</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nnx-xT/</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>0</v>
+      </c>
+      <c r="E346" t="n">
+        <v>9</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/hGx--j/</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D347" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" t="n">
+        <v>9</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:13:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>http://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/dhxxjL/</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D348" t="n">
+        <v>0</v>
+      </c>
+      <c r="E348" t="n">
+        <v>9</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-08-23 12:13:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/sBPx-/</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>0</v>
+      </c>
+      <c r="E349" t="n">
+        <v>10</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:39:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/RBPxx/</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>0</v>
+      </c>
+      <c r="E350" t="n">
+        <v>10</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:39:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/CqPAj/</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="n">
+        <v>10</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:39:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/CdPA-/</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" t="n">
+        <v>10</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:39:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dGPAz/</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>0</v>
+      </c>
+      <c r="E353" t="n">
+        <v>10</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:39:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/CqPAL/</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
+        <v>10</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:40:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/ndjww/</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>10</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:40:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/CKPAP/</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>10</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:41:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/GnPAP/</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" t="n">
+        <v>10</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:41:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/CdPAT/</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>0</v>
+      </c>
+      <c r="E358" t="n">
+        <v>10</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:41:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/hCjwj/</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>0</v>
+      </c>
+      <c r="E359" t="n">
+        <v>10</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:44:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/hhjwj/</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>0</v>
+      </c>
+      <c r="E360" t="n">
+        <v>10</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:44:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/hKjwj/</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>0</v>
+      </c>
+      <c r="E361" t="n">
+        <v>10</v>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:44:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/hKTxj/</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>0</v>
+      </c>
+      <c r="E362" t="n">
+        <v>10</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:44:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/ndTxo/</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>0</v>
+      </c>
+      <c r="E363" t="n">
+        <v>10</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:44:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Rdjwx/</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>0</v>
+      </c>
+      <c r="E364" t="n">
+        <v>10</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:44:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GGTx-/</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>10</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:45:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/qhjwA/</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" t="n">
+        <v>10</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:45:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/CGTx-/</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>0</v>
+      </c>
+      <c r="E367" t="n">
+        <v>10</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:45:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/KRjwA/</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>0</v>
+      </c>
+      <c r="E368" t="n">
+        <v>10</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:45:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/hsTxx/</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>0</v>
+      </c>
+      <c r="E369" t="n">
+        <v>10</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:45:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nBTAw/</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>0</v>
+      </c>
+      <c r="E370" t="n">
+        <v>10</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:46:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/dsTxA/</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>0</v>
+      </c>
+      <c r="E371" t="n">
+        <v>10</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:46:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/Ksx-Lj/</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" t="n">
+        <v>10</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:46:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GqLTj/</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>0</v>
+      </c>
+      <c r="E373" t="n">
+        <v>10</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:51:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/RqLTA/</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>0</v>
+      </c>
+      <c r="E374" t="n">
+        <v>10</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:53:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/sGjTx/</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>0</v>
+      </c>
+      <c r="E375" t="n">
+        <v>10</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:53:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/CnTAo/</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>10</v>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:53:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/hdTAA/</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>0</v>
+      </c>
+      <c r="E377" t="n">
+        <v>10</v>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:53:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/RnLzP/</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>0</v>
+      </c>
+      <c r="E378" t="n">
+        <v>10</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:53:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/hqLTw/</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>10</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>2026-08-23 16:53:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/qsx-To/</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>0</v>
+      </c>
+      <c r="E380" t="n">
+        <v>10</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:03:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/qBjLw/</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>0</v>
+      </c>
+      <c r="E381" t="n">
+        <v>10</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/KGoPL/</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>0</v>
+      </c>
+      <c r="E382" t="n">
+        <v>10</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/qB-Tz/</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>0</v>
+      </c>
+      <c r="E383" t="n">
+        <v>10</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:04:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/Gn-P/</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>0</v>
+      </c>
+      <c r="E384" t="n">
+        <v>10</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:04:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/RC-j/</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>0</v>
+      </c>
+      <c r="E385" t="n">
+        <v>10</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:04:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/CG-Tz/</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>0</v>
+      </c>
+      <c r="E386" t="n">
+        <v>10</v>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:04:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nq-P/</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" t="n">
+        <v>10</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:04:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/RK-j/</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>0</v>
+      </c>
+      <c r="E388" t="n">
+        <v>10</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:04:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/sh-Tw/</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" t="n">
+        <v>10</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:04:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/hs-Tw/</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" t="n">
+        <v>10</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nd-o/</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>0</v>
+      </c>
+      <c r="E391" t="n">
+        <v>10</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:04:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/Kqoj/</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>0</v>
+      </c>
+      <c r="E392" t="n">
+        <v>10</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:06:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nBoT/</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" t="n">
+        <v>10</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:06:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nsoo/</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" t="n">
+        <v>10</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:07:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/KGo-/</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>0</v>
+      </c>
+      <c r="E395" t="n">
+        <v>10</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:07:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/CG-w/</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>0</v>
+      </c>
+      <c r="E396" t="n">
+        <v>10</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:08:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Rs-TT/</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" t="n">
+        <v>10</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:08:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/qG-TT/</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>0</v>
+      </c>
+      <c r="E398" t="n">
+        <v>10</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:08:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/qK-T/</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>0</v>
+      </c>
+      <c r="E399" t="n">
+        <v>10</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:08:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Rh-TA/</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>0</v>
+      </c>
+      <c r="E400" t="n">
+        <v>10</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:08:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/KK-TA/</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" t="n">
+        <v>10</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nKow/</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>0</v>
+      </c>
+      <c r="E402" t="n">
+        <v>10</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:10:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/nd-Lw/</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" t="n">
+        <v>10</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:10:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/sqjo/</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>10</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:10:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/hd-Lz/</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>0</v>
+      </c>
+      <c r="E405" t="n">
+        <v>10</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:11:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/hB-LT/</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>0</v>
+      </c>
+      <c r="E406" t="n">
+        <v>10</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dd-LL/</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="n">
+        <v>10</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GnjL/</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" t="n">
+        <v>10</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/sn-Lo/</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="n">
+        <v>10</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:14:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/hhPA/</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="n">
+        <v>10</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:14:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/sB-Lx/</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" t="n">
+        <v>10</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:15:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dd-Lx/</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>0</v>
+      </c>
+      <c r="E412" t="n">
+        <v>10</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Kd-LA/</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="n">
+        <v>10</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:16:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/qBPo/</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="n">
+        <v>10</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dq-L-/</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>0</v>
+      </c>
+      <c r="E415" t="n">
+        <v>10</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nKPT/</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" t="n">
+        <v>10</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:17:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/sR-Pw/</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" t="n">
+        <v>10</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:17:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/RC-P-/</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" t="n">
+        <v>10</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:17:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Gd-P-/</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>10</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:17:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/KRLo/</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>0</v>
+      </c>
+      <c r="E420" t="n">
+        <v>10</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:17:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/dGLo/</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" t="n">
+        <v>10</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:17:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/sh-P-/</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>0</v>
+      </c>
+      <c r="E422" t="n">
+        <v>10</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:17:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dG-Pz/</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>0</v>
+      </c>
+      <c r="E423" t="n">
+        <v>10</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:17:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dC-Pz/</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" t="n">
+        <v>10</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/hBPw/</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>0</v>
+      </c>
+      <c r="E425" t="n">
+        <v>10</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nRPz/</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="n">
+        <v>10</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/RRPw/</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="n">
+        <v>10</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/CBPz/</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="n">
+        <v>10</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/sG-Pz/</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="n">
+        <v>10</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/qs-PT/</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="n">
+        <v>10</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/dhLx/</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>0</v>
+      </c>
+      <c r="E431" t="n">
+        <v>10</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/KdLx/</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>0</v>
+      </c>
+      <c r="E432" t="n">
+        <v>10</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/ns-PL/</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>0</v>
+      </c>
+      <c r="E433" t="n">
+        <v>10</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:18:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/qR-PA/</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>0</v>
+      </c>
+      <c r="E434" t="n">
+        <v>10</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:22:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/nC-PA/</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" t="n">
+        <v>10</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:23:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/RB-jw/</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>0</v>
+      </c>
+      <c r="E436" t="n">
+        <v>10</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:23:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/GB-jw/</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>0</v>
+      </c>
+      <c r="E437" t="n">
+        <v>10</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:23:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/RGTo/</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>0</v>
+      </c>
+      <c r="E438" t="n">
+        <v>10</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:23:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GBTo/</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>0</v>
+      </c>
+      <c r="E439" t="n">
+        <v>10</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:23:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Gs-jz/</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>0</v>
+      </c>
+      <c r="E440" t="n">
+        <v>10</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:23:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/CK-jz/</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>0</v>
+      </c>
+      <c r="E441" t="n">
+        <v>10</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:24:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Gd-jT/</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>0</v>
+      </c>
+      <c r="E442" t="n">
+        <v>10</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:24:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/CsTP/</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>0</v>
+      </c>
+      <c r="E443" t="n">
+        <v>10</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:24:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Kq-jL/</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>0</v>
+      </c>
+      <c r="E444" t="n">
+        <v>10</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:25:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/qGTz/</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>0</v>
+      </c>
+      <c r="E445" t="n">
+        <v>10</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:25:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/GG-jL/</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>0</v>
+      </c>
+      <c r="E446" t="n">
+        <v>10</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:25:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nGTL/</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>0</v>
+      </c>
+      <c r="E447" t="n">
+        <v>10</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:25:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/dn-jP/</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>0</v>
+      </c>
+      <c r="E448" t="n">
+        <v>10</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:25:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/qBTT/</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>0</v>
+      </c>
+      <c r="E449" t="n">
+        <v>10</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/nBzP/</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>0</v>
+      </c>
+      <c r="E450" t="n">
+        <v>10</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/hR-oz/</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>0</v>
+      </c>
+      <c r="E451" t="n">
+        <v>10</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/RK-jj/</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>0</v>
+      </c>
+      <c r="E452" t="n">
+        <v>10</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/GK-j-/</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>0</v>
+      </c>
+      <c r="E453" t="n">
+        <v>10</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Rh-jx/</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>0</v>
+      </c>
+      <c r="E454" t="n">
+        <v>10</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/GCzx/</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>0</v>
+      </c>
+      <c r="E455" t="n">
+        <v>10</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/ss-jx/</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>0</v>
+      </c>
+      <c r="E456" t="n">
+        <v>10</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes-anexos/qqz-/</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>0</v>
+      </c>
+      <c r="E457" t="n">
+        <v>10</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/licitacoes/Gh-jA/</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>0</v>
+      </c>
+      <c r="E458" t="n">
+        <v>10</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:26:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KRTP/</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>0</v>
+      </c>
+      <c r="E459" t="n">
+        <v>10</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:27:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Ks-A-/</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>0</v>
+      </c>
+      <c r="E460" t="n">
+        <v>10</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:27:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KGTw/</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>0</v>
+      </c>
+      <c r="E461" t="n">
+        <v>10</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:30:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ChTw/</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E462" t="n">
+        <v>10</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:30:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GszA/</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>0</v>
+      </c>
+      <c r="E463" t="n">
+        <v>10</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:30:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CKzx/</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>0</v>
+      </c>
+      <c r="E464" t="n">
+        <v>10</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:30:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KRzx/</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>0</v>
+      </c>
+      <c r="E465" t="n">
+        <v>10</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:30:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GBPoT/</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>0</v>
+      </c>
+      <c r="E466" t="n">
+        <v>10</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:30:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hhPoz/</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>0</v>
+      </c>
+      <c r="E467" t="n">
+        <v>10</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:30:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ndPjA/</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>0</v>
+      </c>
+      <c r="E468" t="n">
+        <v>10</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Rnz-/</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>0</v>
+      </c>
+      <c r="E469" t="n">
+        <v>10</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qqzo/</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>0</v>
+      </c>
+      <c r="E470" t="n">
+        <v>10</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sCzj/</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>0</v>
+      </c>
+      <c r="E471" t="n">
+        <v>10</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dCzj/</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>0</v>
+      </c>
+      <c r="E472" t="n">
+        <v>10</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KnzP/</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>0</v>
+      </c>
+      <c r="E473" t="n">
+        <v>10</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GKPjx/</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>0</v>
+      </c>
+      <c r="E474" t="n">
+        <v>10</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KqPjx/</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>0</v>
+      </c>
+      <c r="E475" t="n">
+        <v>10</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hBzz/</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>0</v>
+      </c>
+      <c r="E476" t="n">
+        <v>10</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sBzz/</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>0</v>
+      </c>
+      <c r="E477" t="n">
+        <v>10</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/Cqzw/</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>0</v>
+      </c>
+      <c r="E478" t="n">
+        <v>10</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KdwA/</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>0</v>
+      </c>
+      <c r="E479" t="n">
+        <v>10</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dKwP/</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>0</v>
+      </c>
+      <c r="E480" t="n">
+        <v>10</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GdwP/</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>0</v>
+      </c>
+      <c r="E481" t="n">
+        <v>10</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/KswL/</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>0</v>
+      </c>
+      <c r="E482" t="n">
+        <v>10</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:32:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sdwz/</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>0</v>
+      </c>
+      <c r="E483" t="n">
+        <v>10</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/ndwz/</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>0</v>
+      </c>
+      <c r="E484" t="n">
+        <v>10</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dGww/</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>0</v>
+      </c>
+      <c r="E485" t="n">
+        <v>10</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RRPjL/</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>0</v>
+      </c>
+      <c r="E486" t="n">
+        <v>10</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/snxAA/</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>0</v>
+      </c>
+      <c r="E487" t="n">
+        <v>10</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RdxAA/</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>0</v>
+      </c>
+      <c r="E488" t="n">
+        <v>10</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CCxAx/</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>0</v>
+      </c>
+      <c r="E489" t="n">
+        <v>10</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sBxAx/</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>0</v>
+      </c>
+      <c r="E490" t="n">
+        <v>10</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CBPjT/</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>0</v>
+      </c>
+      <c r="E491" t="n">
+        <v>10</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/GqPjT/</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>0</v>
+      </c>
+      <c r="E492" t="n">
+        <v>10</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RGPjz/</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>0</v>
+      </c>
+      <c r="E493" t="n">
+        <v>10</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/sdPjw/</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>0</v>
+      </c>
+      <c r="E494" t="n">
+        <v>10</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/dRPjw/</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>0</v>
+      </c>
+      <c r="E495" t="n">
+        <v>10</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/qBPPA/</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>0</v>
+      </c>
+      <c r="E496" t="n">
+        <v>10</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hhPPx/</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>0</v>
+      </c>
+      <c r="E497" t="n">
+        <v>10</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/RBxAo/</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>0</v>
+      </c>
+      <c r="E498" t="n">
+        <v>10</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/CdxAo/</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>0</v>
+      </c>
+      <c r="E499" t="n">
+        <v>10</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:35:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hdxAT/</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>0</v>
+      </c>
+      <c r="E500" t="n">
+        <v>10</v>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:36:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>santoantoniodoparaiso</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://www.pmsantoantoniodoparaiso.pr.gov.br/portal/download/legislacao/hRTL/</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>0</v>
+      </c>
+      <c r="E501" t="n">
+        <v>10</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>2026-08-23 17:36:32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
